--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/risk_control_register.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/risk_control_register.xlsx
@@ -497,12 +497,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data privacy 0</t>
+          <t>Vendor due diligence 0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SoD 1</t>
+          <t>Payment auth 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -576,27 +576,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Payment auth 2</t>
+          <t>Vendor due diligence 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -608,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Access review 3</t>
+          <t>Change mgmt 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -645,32 +645,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Payment auth 4</t>
+          <t>SoD 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Access review 5</t>
+          <t>Model validation 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reconciliation 6</t>
+          <t>Backup 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -734,17 +734,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monitoring 8</t>
+          <t>Reconciliation 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vendor due diligence 9</t>
+          <t>Data privacy 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Access review 10</t>
+          <t>SoD 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -904,22 +904,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Payment auth 11</t>
+          <t>Monitoring 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -978,22 +978,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Access review 13</t>
+          <t>Change mgmt 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Backup 14</t>
+          <t>Payment auth 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Data privacy 15</t>
+          <t>Payment auth 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1089,32 +1089,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Backup 16</t>
+          <t>Vendor due diligence 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -1163,17 +1163,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SoD 18</t>
+          <t>Payment auth 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SoD 19</t>
+          <t>Reconciliation 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Backup 20</t>
+          <t>Change mgmt 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Change mgmt 21</t>
+          <t>SoD 21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Backup 22</t>
+          <t>Payment auth 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SoD 23</t>
+          <t>Backup 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1385,32 +1385,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Model validation 24</t>
+          <t>Access review 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -1496,32 +1496,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Model validation 27</t>
+          <t>Payment auth 27</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monitoring 28</t>
+          <t>Backup 28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1580,22 +1580,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -1607,22 +1607,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monitoring 30</t>
+          <t>Model validation 30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SoD 31</t>
+          <t>Vendor due diligence 31</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1659,17 +1659,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vendor due diligence 32</t>
+          <t>Access review 32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1718,22 +1718,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Change mgmt 33</t>
+          <t>Data privacy 33</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -1760,27 +1760,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Change mgmt 34</t>
+          <t>Vendor due diligence 34</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vendor due diligence 36</t>
+          <t>Payment auth 36</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Payment auth 37</t>
+          <t>Vendor due diligence 37</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Payment auth 38</t>
+          <t>Vendor due diligence 38</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reconciliation 39</t>
+          <t>Payment auth 39</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Backup 40</t>
+          <t>SoD 40</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vendor due diligence 41</t>
+          <t>SoD 41</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -2093,27 +2093,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Change mgmt 43</t>
+          <t>Payment auth 43</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Change mgmt 44</t>
+          <t>Monitoring 44</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2140,17 +2140,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Change mgmt 45</t>
+          <t>Access review 45</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -2199,22 +2199,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Backup 46</t>
+          <t>Access review 46</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Data privacy 48</t>
+          <t>Access review 48</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monitoring 49</t>
+          <t>Payment auth 49</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Data privacy 50</t>
+          <t>Payment auth 50</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monitoring 51</t>
+          <t>Reconciliation 51</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Access review 52</t>
+          <t>Vendor due diligence 52</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Change mgmt 53</t>
+          <t>Reconciliation 53</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -2495,27 +2495,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Change mgmt 54</t>
+          <t>Reconciliation 54</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monitoring 57</t>
+          <t>SoD 57</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Data privacy 58</t>
+          <t>Access review 58</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -2680,27 +2680,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Backup 59</t>
+          <t>Change mgmt 59</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Backup 60</t>
+          <t>Access review 60</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Payment auth 61</t>
+          <t>Backup 61</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Model validation 62</t>
+          <t>Payment auth 62</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -2828,32 +2828,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Data privacy 63</t>
+          <t>Monitoring 63</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Change mgmt 64</t>
+          <t>Monitoring 64</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vendor due diligence 67</t>
+          <t>Data privacy 67</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Backup 69</t>
+          <t>Payment auth 69</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Model validation 70</t>
+          <t>Monitoring 70</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monitoring 71</t>
+          <t>Change mgmt 71</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3139,17 +3139,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Access review 72</t>
+          <t>Data privacy 72</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3176,17 +3176,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -3203,27 +3203,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Data privacy 73</t>
+          <t>Reconciliation 73</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reconciliation 74</t>
+          <t>SoD 74</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -3272,32 +3272,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vendor due diligence 75</t>
+          <t>SoD 75</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Backup 76</t>
+          <t>Access review 76</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vendor due diligence 77</t>
+          <t>Data privacy 77</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Change mgmt 78</t>
+          <t>SoD 78</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -3420,32 +3420,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SoD 79</t>
+          <t>Monitoring 79</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Model validation 80</t>
+          <t>Change mgmt 80</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -3494,17 +3494,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Backup 81</t>
+          <t>Payment auth 81</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monitoring 82</t>
+          <t>Access review 82</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3546,17 +3546,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -3568,32 +3568,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Reconciliation 83</t>
+          <t>Data privacy 83</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Data privacy 84</t>
+          <t>Change mgmt 84</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3642,17 +3642,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SoD 85</t>
+          <t>Payment auth 85</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monitoring 86</t>
+          <t>Change mgmt 86</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -3716,22 +3716,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monitoring 87</t>
+          <t>Reconciliation 87</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Change mgmt 88</t>
+          <t>SoD 88</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -3795,27 +3795,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Payment auth 89</t>
+          <t>Vendor due diligence 89</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -3827,12 +3827,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Payment auth 90</t>
+          <t>Model validation 90</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3864,32 +3864,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Vendor due diligence 91</t>
+          <t>Data privacy 91</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3901,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SoD 92</t>
+          <t>Reconciliation 92</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Payment auth 93</t>
+          <t>Model validation 93</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reconciliation 94</t>
+          <t>Model validation 94</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Change mgmt 95</t>
+          <t>Access review 95</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SoD 96</t>
+          <t>Vendor due diligence 96</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4086,32 +4086,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Payment auth 97</t>
+          <t>Change mgmt 97</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4123,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Backup 98</t>
+          <t>Change mgmt 98</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Access review 99</t>
+          <t>Model validation 99</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Change mgmt 100</t>
+          <t>Data privacy 100</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Model validation 101</t>
+          <t>Payment auth 101</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Payment auth 102</t>
+          <t>Data privacy 102</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -4308,22 +4308,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Backup 103</t>
+          <t>SoD 103</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Data privacy 104</t>
+          <t>SoD 104</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -4382,17 +4382,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Model validation 105</t>
+          <t>Change mgmt 105</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -4419,22 +4419,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vendor due diligence 106</t>
+          <t>SoD 106</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -4456,32 +4456,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Access review 107</t>
+          <t>Vendor due diligence 107</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Data privacy 108</t>
+          <t>Backup 108</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -4530,27 +4530,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vendor due diligence 109</t>
+          <t>Model validation 109</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Reconciliation 110</t>
+          <t>Monitoring 110</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Payment auth 111</t>
+          <t>SoD 111</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Vendor due diligence 112</t>
+          <t>Access review 112</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Vendor due diligence 113</t>
+          <t>Backup 113</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4693,17 +4693,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4725,22 +4725,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SoD 115</t>
+          <t>Change mgmt 115</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4767,17 +4767,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
     </row>
@@ -4789,12 +4789,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SoD 116</t>
+          <t>Monitoring 116</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Model validation 117</t>
+          <t>Data privacy 117</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>David Chen</t>
         </is>
       </c>
     </row>
@@ -4863,32 +4863,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SOX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Payment auth 118</t>
+          <t>SoD 118</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOX</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monitoring 119</t>
+          <t>Model validation 119</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
     </row>
